--- a/data/Step2_Workflow 명세서 외 기타 설계문서들_양식.xlsx
+++ b/data/Step2_Workflow 명세서 외 기타 설계문서들_양식.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\1. 강의\1.4 기타\AIVLE 과정\AIVLE 시즌2\강의준비\9기\5.미프2_멀티 에이전트_운영시스템\에이블러용\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\1. 강의\1.4 기타\AIVLE 과정\AIVLE 시즌2\강의준비\9기\5.미프2_멀티 에이전트_운영시스템\실습파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D9353B-E287-498C-9A38-402BC532CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F7A9F8-D88F-449F-828A-4B29341ABB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="738" activeTab="3" xr2:uid="{37563ECD-362D-43B2-A1B8-113A38767F2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="738" xr2:uid="{37563ECD-362D-43B2-A1B8-113A38767F2D}"/>
   </bookViews>
   <sheets>
     <sheet name="workflow 명세서" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
   <si>
     <t>내용</t>
   </si>
@@ -51,6 +51,45 @@
     <t>역할</t>
   </si>
   <si>
+    <t>str</t>
+  </si>
+  <si>
+    <t>Overwrite</t>
+  </si>
+  <si>
+    <t>분기</t>
+  </si>
+  <si>
+    <t>종료</t>
+  </si>
+  <si>
+    <t>critic</t>
+  </si>
+  <si>
+    <t>Overwrite(초기 입력)</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>초기 실행 제어</t>
+  </si>
+  <si>
+    <t>Critic 실행</t>
+  </si>
+  <si>
+    <t>Critic 평가 수행</t>
+  </si>
+  <si>
+    <t>프로세스 종료</t>
+  </si>
+  <si>
+    <t>Critic → Supervisor → END</t>
+  </si>
+  <si>
     <t>Key</t>
   </si>
   <si>
@@ -66,6 +105,45 @@
     <t>사용 Agent</t>
   </si>
   <si>
+    <t>분석 대상이 되는 상품 리뷰 원문 텍스트</t>
+  </si>
+  <si>
+    <t>Analyzer, Supervisor</t>
+  </si>
+  <si>
+    <t>analyzer_result</t>
+  </si>
+  <si>
+    <t>Optional[Dict[str, Any]]</t>
+  </si>
+  <si>
+    <t>Analyzer, Critic, Supervisor</t>
+  </si>
+  <si>
+    <t>critic_result</t>
+  </si>
+  <si>
+    <t>retry_count</t>
+  </si>
+  <si>
+    <t>현재까지 재시도한 횟수</t>
+  </si>
+  <si>
+    <t>max_retries</t>
+  </si>
+  <si>
+    <t>허용 가능한 최대 재시도 횟수</t>
+  </si>
+  <si>
+    <t>next_agent</t>
+  </si>
+  <si>
+    <t>Supervisor가 결정한 다음 실행 Agent</t>
+  </si>
+  <si>
+    <t>Literal["analyzer", "critic", "end"]</t>
+  </si>
+  <si>
     <t>구분</t>
   </si>
   <si>
@@ -87,6 +165,51 @@
     <t>구현 방식</t>
   </si>
   <si>
+    <t>Analyzer 실행</t>
+  </si>
+  <si>
+    <t>analyzer_result is None</t>
+  </si>
+  <si>
+    <t>아직 리뷰 분석 결과가 없으면 먼저 Analyzer를 호출하여 속성/감성 분석을 수행</t>
+  </si>
+  <si>
+    <t>Analyzer 실행 시작</t>
+  </si>
+  <si>
+    <t>START → Supervisor → Analyzer</t>
+  </si>
+  <si>
+    <t>검수 단계 진입</t>
+  </si>
+  <si>
+    <t>analyzer_result is not None AND critic_result is None</t>
+  </si>
+  <si>
+    <t>Analyzer 결과는 존재하지만 아직 검수가 수행되지 않은 경우 Critic을 호출하여 결과 적합성 판단</t>
+  </si>
+  <si>
+    <t>Analyzer → Supervisor → Critic</t>
+  </si>
+  <si>
+    <t>적합 판정 종료</t>
+  </si>
+  <si>
+    <t>critic_result.verdict</t>
+  </si>
+  <si>
+    <t>critic_result["verdict"] == "적합"</t>
+  </si>
+  <si>
+    <t>재분석 제어</t>
+  </si>
+  <si>
+    <t>Analyzer 재실행</t>
+  </si>
+  <si>
+    <t>Critic → Supervisor → Analyzer</t>
+  </si>
+  <si>
     <t>Agent</t>
   </si>
   <si>
@@ -96,6 +219,24 @@
     <t>출력 형식 및 예시</t>
   </si>
   <si>
+    <t>analyzer</t>
+  </si>
+  <si>
+    <t>상품 리뷰에서 속성 및 감성을 추출</t>
+  </si>
+  <si>
+    <t>Analyzer</t>
+  </si>
+  <si>
+    <t>DB 저장</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>- review</t>
+  </si>
+  <si>
     <t>각 단계</t>
   </si>
   <si>
@@ -106,6 +247,279 @@
   </si>
   <si>
     <t>출력</t>
+  </si>
+  <si>
+    <t>Critic</t>
+  </si>
+  <si>
+    <t>- state</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>Analyzer가 추출한 속성/감성 분석 결과. 예: {"items":[{"aspect":"보습","label":1,"evidence":"보습력이 좋아요"}]}</t>
+  </si>
+  <si>
+    <t>Critic의 검토 결과. 예: `{"verdict":"적합</t>
+  </si>
+  <si>
+    <t>부적합","reason":"..."}`</t>
+  </si>
+  <si>
+    <t>reason_code</t>
+  </si>
+  <si>
+    <t>Supervisor가 Critic의 부적합 사유를 표준 코드로 분류한 값. OUTPUT_ERROR / SCOPE_ERROR / EVIDENCE_ERROR / QUALITY_ERROR / OK 중 하나</t>
+  </si>
+  <si>
+    <t>Optional[Literal["OUTPUT_ERROR", "SCOPE_ERROR", "EVIDENCE_ERROR", "QUALITY_ERROR", "OK"]]</t>
+  </si>
+  <si>
+    <t>repair_directive</t>
+  </si>
+  <si>
+    <t>재시도 시 Analyzer가 참고할 짧은 수정 지시문. 예: "근거 문구를 반드시 포함하고 aspect는 4개 범위만 사용"</t>
+  </si>
+  <si>
+    <t>Optional[str]</t>
+  </si>
+  <si>
+    <t>Supervisor, Analyzer</t>
+  </si>
+  <si>
+    <t>Critic이 분석 결과를 적합하다고 판단한 경우, reason_code="OK"와 빈 repair_directive를 기록하고 종료</t>
+  </si>
+  <si>
+    <t>부적합 사유 분류</t>
+  </si>
+  <si>
+    <t>critic_result.reason</t>
+  </si>
+  <si>
+    <t>reason_code / repair_directive 생성</t>
+  </si>
+  <si>
+    <t>critic_result["verdict"] != "적합"</t>
+  </si>
+  <si>
+    <t>Critic이 부적합으로 판단한 경우, Supervisor가 critic_result.reason을 바탕으로 reason_code를 분류하고 재분석용 repair_directive를 생성</t>
+  </si>
+  <si>
+    <t>부적합 사유 표준화</t>
+  </si>
+  <si>
+    <t>Critic → Supervisor</t>
+  </si>
+  <si>
+    <t>reason_code, retry_count, max_retries</t>
+  </si>
+  <si>
+    <t>reason_code in RETRYABLE AND retry_count &lt; max_retries</t>
+  </si>
+  <si>
+    <t>재시도 가능한 오류인 경우, 수정 지시를 반영해 Analyzer를 다시 실행. 이때 retry_count를 1 증가시키고 analyzer_result, critic_result를 초기화</t>
+  </si>
+  <si>
+    <t>재분석 수행 / 수정 지시 반영</t>
+  </si>
+  <si>
+    <t>재시도 불가 종료</t>
+  </si>
+  <si>
+    <t>reason_code not in RETRYABLE OR retry_count &gt;= max_retries</t>
+  </si>
+  <si>
+    <t>재시도 대상이 아니거나 최대 재시도 횟수에 도달한 경우 더 이상 재분석하지 않고 현재 결과 기준 종료</t>
+  </si>
+  <si>
+    <t>의미</t>
+  </si>
+  <si>
+    <t>Supervisor 처리</t>
+  </si>
+  <si>
+    <t>OUTPUT_ERROR</t>
+  </si>
+  <si>
+    <t>출력 형식, items 구조, label 범위 등 형식 오류</t>
+  </si>
+  <si>
+    <t>수정 지시 생성 후 재시도 가능</t>
+  </si>
+  <si>
+    <t>SCOPE_ERROR</t>
+  </si>
+  <si>
+    <t>허용되지 않은 aspect 사용 등 범위 오류</t>
+  </si>
+  <si>
+    <t>EVIDENCE_ERROR</t>
+  </si>
+  <si>
+    <t>evidence가 리뷰 원문과 맞지 않음</t>
+  </si>
+  <si>
+    <t>QUALITY_ERROR</t>
+  </si>
+  <si>
+    <t>그 외 품질 문제</t>
+  </si>
+  <si>
+    <t>수정 지시 생성 후 재시도 가능 여부 정책에 따름</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Critic 적합 판정</t>
+  </si>
+  <si>
+    <t>{"items":[{"aspect":"가격","label":0,"evidence":"가격이 조금 비싸요"},{"aspect":"포장","label":1,"evidence":"포장이 깔끔했어요"}]}</t>
+  </si>
+  <si>
+    <t>분석 결과의 적합성을 검수</t>
+  </si>
+  <si>
+    <t>{"verdict":"부적합","reason":"evidence가 리뷰 원문과 일치하지 않음"}</t>
+  </si>
+  <si>
+    <t>- 리뷰에서 언급된 속성만 추출
+- 허용 속성은 보습, 가격, 향, 포장만 사용
+- 속성이 없으면 items는 빈 리스트로 작성
+- label은 0 또는 1만 사용
+- 같은 aspect는 1회만 출력
+- evidence는 해당 속성을 가장 잘 보여주는 대표 근거 1개만 작성
+- Step2에서는 Supervisor가 준 repair_directive를 반영하여 재분석 수행 가능
+- 출력은 파이썬 dict 1개만 작성- 설명, 코드블록, 마크다운 금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>Critic의 부적합 사유를 표준 reason_code로 분류하고 수정 지시 생성</t>
+  </si>
+  <si>
+    <t>{"reason_code":"OUTPUT_ERROR","repair_directive":"dict 형식과 items 구조를 맞춰라."}</t>
+  </si>
+  <si>
+    <t>- 입력: 원문 리뷰 + analyzer 결과- 분석 결과를 적합 / 부적합으로 판정
+- 적합: 리뷰 내용과 일치하고 evidence가 리뷰에서 확인 가능
+- 부적합: 리뷰에 없는 내용을 추가했거나, aspect / label / evidence가 부정확함
+- 애매하면 부적합으로 보수적으로 판정
+- 출력은 파이썬 dict 1개만 작성
+- verdict는 반드시 적합 / 부적합 중 하나만 사용
+- reason은 짧고 핵심만 작성
+- 설명, 코드블록, 마크다운 금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 입력: critic_result.reason
+- 부적합 사유를 아래 코드 중 하나만 선택
+  • OUTPUT_ERROR
+  • SCOPE_ERROR
+  • EVIDENCE_ERROR
+  • QUALITY_ERROR
+- 분류 기준  
+  • OUTPUT_ERROR: 출력 형식, items 구조, label 범위 등 형식 문제
+  • SCOPE_ERROR: 허용되지 않은 aspect 사용
+  • EVIDENCE_ERROR: evidence가 리뷰 원문과 맞지 않음
+  • QUALITY_ERROR: 그 외 품질 문제- 가장 직접적인 원인 1개만 선택
+- 애매하면 QUALITY_ERROR로 분류
+- repair_directive에 재분석용 짧은 수정 지시 작성
+- 출력은 파이썬 dict 1개만 작성
+- 설명, 코드블록, 마크다운 금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시보드</t>
+  </si>
+  <si>
+    <t>- DB 데이터</t>
+  </si>
+  <si>
+    <t>- 저장된 결과 조회 및 시각화</t>
+  </si>
+  <si>
+    <t>- 분석 결과 화면</t>
+  </si>
+  <si>
+    <t>- 사용자가 리뷰 입력
+- 초기 State 생성 (retry_count=0, max_retries 설정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 현재 상태 확인
+- analyzer_result 없으면 Analyzer 호출
+- analyzer_result 있고 critic_result 없으면 Critic 호출
+- critic_result 확인 후 분기 처리
+① 적합 → 종료
+② 부적합 → reason_code 분류 + repair_directive 생성
+③ 재시도 가능 → retry_count 증가 후 Analyzer 재호출
+④ 재시도 불가 → 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 리뷰에서 속성(aspect) 추출
+- 각 속성에 대한 감성(label) 판단
+- evidence 생성
+- (Step2) repair_directive 반영하여 수정된 결과 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- analyzer_result 검증
+- 리뷰와 일치 여부 판단
+- 적합/부적합 판정 및 사유 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 최종 결과 저장
+- 리뷰 + 분석 결과 + 검수 결과 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- next_agent 
+("analyzer" / "critic" / "end")
+- reason_code
+- repair_directive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- analyzer_result
+{"items":[{"aspect":...,"label":...,"evidence":...}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- critic_result
+{"verdict":"적합/부적합","reason":"..."}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review 
+- analyzer_result
+- critic_result
+- reason_code
+- repair_directive
+- retry_count
+- max_retries</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- repair_directive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- analyzer_result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- analyzer_result
+- critic_result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -321,7 +735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -376,18 +790,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -409,6 +811,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -424,6 +835,1903 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>313763</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>479240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>894787</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1034804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="타원 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96292E8A-46F1-47F3-B2D3-09BED2E40328}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2162734" y="703358"/>
+          <a:ext cx="581024" cy="555564"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Start</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1892865</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>422778</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2552662</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2728481</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="직사각형 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCDB2572-9164-4A93-80AB-85F3707200FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5994218" y="646896"/>
+          <a:ext cx="3304385" cy="2305703"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="30AEAA"/>
+          </a:solidFill>
+          <a:prstDash val="sysDot"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1525484</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>381001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>725808</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1131991</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Google Shape;433;p15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79248A91-812E-4CDD-981B-71FF33201412}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3374455" y="605119"/>
+          <a:ext cx="1452706" cy="750990"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="35ADA9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+          <a:headEnd type="none" w="sm" len="sm"/>
+          <a:tailEnd type="none" w="sm" len="sm"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>DB </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>저장</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>173148</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>877091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1625854</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1555234</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Google Shape;433;p15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A213DBA2-E1F6-4D84-9735-8555544D50B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6919089" y="1101209"/>
+          <a:ext cx="1452706" cy="678143"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="35ADA9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+          <a:headEnd type="none" w="sm" len="sm"/>
+          <a:tailEnd type="none" w="sm" len="sm"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Supervisor</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Agent</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2251836</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>381001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>900469</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>422778</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="연결선: 꺾임 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F8F2CD-7F01-44C6-BD24-C58C7349C449}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="48" idx="0"/>
+          <a:endCxn id="47" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5852720" y="-1146794"/>
+          <a:ext cx="41777" cy="3545603"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -547191"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2007914</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1918859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>816032</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2597002</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Google Shape;433;p15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0963F64E-36B6-4123-9A77-530B977DEDD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6109267" y="2142977"/>
+          <a:ext cx="1452706" cy="678143"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="35ADA9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+          <a:headEnd type="none" w="sm" len="sm"/>
+          <a:tailEnd type="none" w="sm" len="sm"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>리뷰 분석</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Agent</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>89680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1555233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>899502</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1918858</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="연결선: 꺾임 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAC8D441-153E-4916-964D-4EC108B6D848}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="49" idx="2"/>
+          <a:endCxn id="52" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7058719" y="1556253"/>
+          <a:ext cx="363625" cy="809822"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>978281</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1918859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2430987</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2597002</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Google Shape;433;p15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F5A6C5D-6DA4-4C7E-A518-23F0B97AB28B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7724222" y="2142977"/>
+          <a:ext cx="1452706" cy="678143"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="35ADA9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+          <a:headEnd type="none" w="sm" len="sm"/>
+          <a:tailEnd type="none" w="sm" len="sm"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>검토</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Agent</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>899501</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1555233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1704634</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1918858</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="연결선: 꺾임 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8AE39AA-A501-461C-9280-FE4911D11602}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="49" idx="2"/>
+          <a:endCxn id="54" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="7866196" y="1558597"/>
+          <a:ext cx="363625" cy="805133"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>725809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>756496</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1892866</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1575630</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="연결선: 꺾임 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C1C25F-C6E2-4FF8-88E5-BFABE4FF4CF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="47" idx="1"/>
+          <a:endCxn id="48" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="4827162" y="980614"/>
+          <a:ext cx="1167057" cy="819134"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2251837</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1131991</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2251838</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1838388</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="57" name="직선 화살표 연결선 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50126C67-FE21-43A2-91C7-C0950F793611}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="48" idx="2"/>
+          <a:endCxn id="60" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4100808" y="1356109"/>
+          <a:ext cx="1" cy="706397"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>962523</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1554824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1855748</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1862601</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="TextBox 5146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5027127-B760-402C-9AFE-3EECBD51E721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5063876" y="1778942"/>
+          <a:ext cx="893225" cy="307777"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>분석 결과</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2639849</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>457642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1803741</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>796196</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D68E830B-358C-4204-AC8C-90F8B7737F73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6741202" y="681760"/>
+          <a:ext cx="1808480" cy="338554"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>리뷰 분석 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>Agent</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1525485</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1838388</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>725809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2589378</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Google Shape;433;p15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA2394C-226F-4722-AB14-66DC2A50B45A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3374456" y="2062506"/>
+          <a:ext cx="1452706" cy="750990"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10889"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="35ADA9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+          <a:headEnd type="none" w="sm" len="sm"/>
+          <a:tailEnd type="none" w="sm" len="sm"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ko-KR"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="1" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>대시보드</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>894787</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>756496</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1525484</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>757022</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="직선 화살표 연결선 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3D79B74-DE49-48D4-990D-AE831969A1BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="46" idx="6"/>
+          <a:endCxn id="48" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2743758" y="980614"/>
+          <a:ext cx="630697" cy="526"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>874302</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2210451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1525485</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2213883</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="직선 화살표 연결선 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6F0491-8D2F-42E2-8E41-4D6DBE1344BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="60" idx="1"/>
+          <a:endCxn id="63" idx="6"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2723273" y="2434569"/>
+          <a:ext cx="651183" cy="3432"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>293278</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1925526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>874302</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2495376</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="타원 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4674F061-3FFE-4354-9778-92C3AAC6FE7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2142249" y="2149644"/>
+          <a:ext cx="581024" cy="569850"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>End</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="Noto Sans KR" panose="020B0200000000000000" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -743,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE784D8C-A46D-4742-8AB5-B85C260B46A1}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.25" style="2" customWidth="1"/>
@@ -753,104 +3061,158 @@
     <col min="5" max="16384" width="15.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4" ht="226.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:7" ht="226.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="17"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="18"/>
+    <row r="11" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="19"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="23"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
@@ -888,24 +3250,6 @@
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:D1"/>
@@ -914,12 +3258,13 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5619BBBE-A06E-4C8E-9F23-99CB5DDE0D7C}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.375" style="2" customWidth="1"/>
@@ -932,62 +3277,156 @@
   <sheetData>
     <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="E3" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="108" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -997,10 +3436,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36ED149D-B54D-431A-BDC2-AB2DF6FAB5C9}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.375" style="1" bestFit="1" customWidth="1"/>
@@ -1013,79 +3452,251 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="E3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H3" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="H4" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="108" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1095,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE203A8-C799-46E0-99D0-43ECDE1CB656}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.375" style="1" customWidth="1"/>
@@ -1107,29 +3718,59 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="270" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1359,13 +4000,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DC3F594-6FE6-43C9-8223-A02867C87F08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07B7A9B3-F098-4F50-BA47-87D8D3240E92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96EAB199-4AE1-4995-95B5-679099BA1445}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7355994C-9DA5-4AE6-ADC0-8F09A351FCDD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8DC154A-6150-4A98-B822-8705491B9109}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C2E74A-4F79-414E-B8B1-438454197B39}"/>
 </file>